--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.4401</v>
+        <v>16.74293</v>
       </c>
       <c r="D2" t="n">
-        <v>16.81605</v>
+        <v>16.41169</v>
       </c>
       <c r="E2" t="n">
-        <v>16.91405</v>
+        <v>16.70692</v>
       </c>
       <c r="F2" t="n">
-        <v>43.14203</v>
+        <v>42.27401</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05039</v>
+        <v>0.04985</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81833</v>
+        <v>1.83202</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.53886</v>
+        <v>16.86685</v>
       </c>
       <c r="D3" t="n">
-        <v>16.79567</v>
+        <v>16.57416</v>
       </c>
       <c r="E3" t="n">
-        <v>16.70469</v>
+        <v>16.77154</v>
       </c>
       <c r="F3" t="n">
-        <v>42.15331</v>
+        <v>41.29683</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05068</v>
+        <v>0.05106</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8876</v>
+        <v>1.80973</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.97367</v>
+        <v>16.675</v>
       </c>
       <c r="D4" t="n">
-        <v>16.40715</v>
+        <v>16.49384</v>
       </c>
       <c r="E4" t="n">
-        <v>16.77985</v>
+        <v>16.61455</v>
       </c>
       <c r="F4" t="n">
-        <v>42.41052</v>
+        <v>42.57723</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05029</v>
+        <v>0.05117</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79366</v>
+        <v>1.83941</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.43637</v>
+        <v>16.80694</v>
       </c>
       <c r="D6" t="n">
-        <v>15.8946</v>
+        <v>15.85677</v>
       </c>
       <c r="E6" t="n">
-        <v>16.28719</v>
+        <v>16.23659</v>
       </c>
       <c r="F6" t="n">
-        <v>21.93521</v>
+        <v>21.52448</v>
       </c>
       <c r="G6" t="n">
-        <v>35.12421</v>
+        <v>34.80716</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.97927</v>
+        <v>16.68382</v>
       </c>
       <c r="D7" t="n">
-        <v>16.08184</v>
+        <v>16.07611</v>
       </c>
       <c r="E7" t="n">
-        <v>16.35209</v>
+        <v>16.14199</v>
       </c>
       <c r="F7" t="n">
-        <v>21.71651</v>
+        <v>21.7325</v>
       </c>
       <c r="G7" t="n">
-        <v>34.88633</v>
+        <v>35.20064</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.83712</v>
+        <v>16.777</v>
       </c>
       <c r="D8" t="n">
-        <v>15.94518</v>
+        <v>16.44428</v>
       </c>
       <c r="E8" t="n">
-        <v>16.33711</v>
+        <v>16.6211</v>
       </c>
       <c r="F8" t="n">
-        <v>21.49385</v>
+        <v>22.04372</v>
       </c>
       <c r="G8" t="n">
-        <v>34.66016</v>
+        <v>34.14867</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60671</v>
+        <v>0.61708</v>
       </c>
       <c r="D10" t="n">
-        <v>1.10228</v>
+        <v>1.12139</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6033500000000001</v>
+        <v>0.61017</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11167</v>
+        <v>1.11242</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59811</v>
+        <v>0.5958599999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>1.11326</v>
+        <v>1.09576</v>
       </c>
     </row>
   </sheetData>
